--- a/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,65</t>
+          <t>-1,61; 0,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,0</t>
+          <t>-2,27; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,3</t>
+          <t>-2,25; 0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,0</t>
+          <t>-1,35; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,2</t>
+          <t>-0,58; 0,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,47</t>
+          <t>-0,15; 0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,5</t>
+          <t>-0,53; 0,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 504,12</t>
+          <t>-84,64; 493,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,65</t>
+          <t>-1,63; 0,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,3</t>
+          <t>-2,3; 0,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,0</t>
+          <t>-1,83; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,82; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,22</t>
+          <t>-0,6; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,55</t>
+          <t>-0,16; 0,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,52</t>
+          <t>-0,5; 0,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-84,64; 493,17</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,64</t>
+          <t>-1,63; 0,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,05; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,29</t>
+          <t>-1,97; 0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,19</t>
+          <t>-0,57; 0,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,53</t>
+          <t>-0,53; 0,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 504,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1009-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,34 +603,20 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4526663825620368</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -629,204 +624,110 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,26</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>2.25645264631388</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-49,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,63; 0,65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,05; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.324356647526493</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6342571339535219</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6469857789011357</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.4997558655685662</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-61,15%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.63366104150985</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.049375880578129</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,63</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,97; 0,3</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6503287125756975</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.214327348112573</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +735,209 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.32494462038868</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4588516664501533</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-0.6114752648260845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,67; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 0,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,21</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>-1.969524858398889</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.626694343106637</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>0.2965797839307554</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3342920129798589</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.2991409311706413</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.7350501956115432</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.665339525327915</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.510379742560022</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.211238215858475</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-44,6%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>122,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 0,2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,16; 0,47</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,53; 0,5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 504,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.127846438792352</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1014829001447876</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.004151924521592727</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.4460050867024692</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.225629570984777</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.01144414450285811</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.57262775857731</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.1576990895385468</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5301811540758652</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1981936775871832</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4718445203981605</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.4971506364993303</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="n">
+        <v>5.041233226372617</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +946,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
